--- a/artfynd/A 30552-2025 artfynd.xlsx
+++ b/artfynd/A 30552-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122577532</v>
+        <v>122577540</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424393</v>
+        <v>424418</v>
       </c>
       <c r="R2" t="n">
-        <v>6698885</v>
+        <v>6698892</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,31 +761,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blockig, oskött, delvi försumpad barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,43 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122577540</v>
+        <v>122577526</v>
       </c>
       <c r="B3" t="n">
-        <v>94766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424418</v>
+        <v>424266</v>
       </c>
       <c r="R3" t="n">
-        <v>6698892</v>
+        <v>6698889</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,6 +862,31 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blockig, oskött, delvi försumpad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -913,19 +903,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122577526</v>
+        <v>122577532</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -956,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424266</v>
+        <v>424393</v>
       </c>
       <c r="R4" t="n">
-        <v>6698889</v>
+        <v>6698885</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1016,17 +1001,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 30552-2025 artfynd.xlsx
+++ b/artfynd/A 30552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122577540</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122577526</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,8 +1041,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122577532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>